--- a/data/trans_orig/IP24_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1256</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11079</t>
+          <t>11541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26955</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14691</t>
+          <t>14839</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29881</t>
+          <t>29366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28698</t>
+          <t>29303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>50658</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17021</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30692</t>
+          <t>30340</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24084</t>
+          <t>24145</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44913</t>
+          <t>44567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>70619</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>29,55%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39245</t>
+          <t>39402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56751</t>
+          <t>56593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46052</t>
+          <t>44887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70344</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91521</t>
+          <t>91949</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120968</t>
+          <t>121830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>50,56%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>6639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17344</t>
+          <t>17467</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11333</t>
+          <t>11594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26402</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>20634</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>779</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>6566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>4560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>14341</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>6068</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4095</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>12106</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19398</t>
+          <t>19272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,9%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18337</t>
+          <t>19224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>33518</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>35458</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42608</t>
+          <t>42114</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63641</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,51%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>33256</t>
+          <t>34125</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49814</t>
+          <t>49323</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34601</t>
+          <t>34226</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51518</t>
+          <t>51783</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71299</t>
+          <t>72859</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94197</t>
+          <t>96093</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,8%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>20802</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13071</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15172</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>30380</t>
+          <t>30707</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9624</t>
+          <t>9164</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1381</t>
+          <t>1375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>9334</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>14031</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>434</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,47 +2335,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,41%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>526</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5777</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>0,83%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,52%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>2190</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>558</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6069</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1643</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>9215</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8680</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3811</t>
+          <t>3483</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13477</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17609</t>
+          <t>18259</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5772</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15673</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12924</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>25899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20562</t>
+          <t>21229</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,2%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20664</t>
+          <t>20719</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>33367</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>32831</t>
+          <t>33152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>43224</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>61915</t>
+          <t>62360</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>36,5%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>13042</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8677</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>834</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11843</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6535</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18285</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19544</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20936</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39685</t>
+          <t>39318</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30163</t>
+          <t>29563</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54829</t>
+          <t>53442</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>18713</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>40106</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>40986</t>
+          <t>41802</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>71686</t>
+          <t>72063</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>66953</t>
+          <t>65544</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>107468</t>
+          <t>104589</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>55292</t>
+          <t>56962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>104045</t>
+          <t>105273</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68590</t>
+          <t>69639</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98078</t>
+          <t>98301</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>133198</t>
+          <t>137608</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>191852</t>
+          <t>192966</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,55%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>46205</t>
+          <t>45460</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131454</t>
+          <t>122451</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27176</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>47148</t>
+          <t>46159</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>79035</t>
+          <t>80229</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>177622</t>
+          <t>172034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14390</t>
+          <t>14697</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>11468</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>28120</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>321</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5253</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>434</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>6556</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8413</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14878</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25245</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>32254</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,12 +4151,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22385</t>
+          <t>21988</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>42511</t>
+          <t>42864</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44015</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>69006</t>
+          <t>70817</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>55817</t>
+          <t>55324</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>74201</t>
+          <t>74228</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>61592</t>
+          <t>58831</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>90544</t>
+          <t>90545</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>122072</t>
+          <t>122922</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>159347</t>
+          <t>159532</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,34%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,64%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9362</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>21339</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>19595</t>
+          <t>20104</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>60616</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>33426</t>
+          <t>34276</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>83767</t>
+          <t>76877</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>27,3%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6833</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>12745</t>
+          <t>13140</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,7 +4565,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4725,7 +4725,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>400</t>
+          <t>383</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>4890</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>934</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>1703</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>8199</t>
+          <t>8336</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4833,12 +4833,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3761</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>14357</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>7187</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19530</t>
+          <t>19318</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -4931,12 +4931,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>17268</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4946,12 +4946,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4966,12 +4966,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>10599</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23487</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18483</t>
+          <t>18621</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>36054</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,59%</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>32617</t>
+          <t>32728</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>47096</t>
+          <t>47259</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5059,12 +5059,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>29002</t>
+          <t>29615</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>44195</t>
+          <t>45211</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5114,12 +5114,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>66248</t>
+          <t>66553</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>87723</t>
+          <t>86659</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,5%</t>
         </is>
       </c>
     </row>
@@ -5157,12 +5157,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5852</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5172,12 +5172,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5192,12 +5192,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11172</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5227,12 +5227,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>9750</t>
+          <t>10028</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>26173</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -5270,12 +5270,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>5655</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5285,12 +5285,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5305,12 +5305,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8198</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5340,12 +5340,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11794</t>
+          <t>11212</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9322</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>21504</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7941</t>
+          <t>8273</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>19876</t>
+          <t>20018</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>20005</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>36208</t>
+          <t>37023</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>43322</t>
+          <t>44346</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>69945</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>77560</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>112251</t>
+          <t>111343</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>130049</t>
+          <t>129066</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>174544</t>
+          <t>171516</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>103042</t>
+          <t>102473</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>142872</t>
+          <t>143446</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>158697</t>
+          <t>157980</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>209502</t>
+          <t>205107</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>277449</t>
+          <t>277411</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>339622</t>
+          <t>338280</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>268651</t>
+          <t>271187</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>332947</t>
+          <t>333424</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>292078</t>
+          <t>296622</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>348752</t>
+          <t>351722</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5889,12 +5889,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>578102</t>
+          <t>585076</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>666709</t>
+          <t>666563</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5924,12 +5924,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>47,6%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -5952,12 +5952,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>100980</t>
+          <t>99593</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>203535</t>
+          <t>197961</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>89355</t>
+          <t>88221</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>140517</t>
+          <t>139811</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>202428</t>
+          <t>198835</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>337048</t>
+          <t>320662</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -6065,12 +6065,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>16576</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>32357</t>
+          <t>32469</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>20831</t>
+          <t>19944</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>39004</t>
+          <t>37937</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>40567</t>
+          <t>40725</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>64144</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2222</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2385</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>785</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5657</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,42%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2581</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>6,06%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3076</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6782</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,57%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3157</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1256</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6359</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21171</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14440</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29566</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11,81%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,18%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>17272</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11541</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27515</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16,53%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>26,34%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21186</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14839</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29366</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29303</t>
+          <t>27951</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50658</t>
+          <t>47799</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29708</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21760</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40285</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>24,3%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>17,8%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32,95%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>23137</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>15965</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>30340</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>22,15%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>15,28%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>23733</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24145</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46069</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56705</t>
+          <t>53441</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44567</t>
+          <t>42912</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>71211</t>
+          <t>65641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>49313</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40415</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>59371</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>40,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33,06%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>48,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>48087</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39402</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56593</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>37,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>54,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57033</t>
+          <t>48698</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44887</t>
+          <t>40826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69808</t>
+          <t>56807</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>105120</t>
+          <t>98011</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91949</t>
+          <t>85834</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121830</t>
+          <t>110600</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16544</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10488</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23704</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>11243</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6639</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>17467</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>10,76%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>10430</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>29197</t>
+          <t>26974</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20634</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39689</t>
+          <t>35508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4879</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2376</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>9796</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2338</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11409</t>
+          <t>6390</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14341</t>
+          <t>12363</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>122252</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>104462</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>102927</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>102927</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>102927</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>136518</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>136518</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>136518</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>327</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>240979</t>
+          <t>225179</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1175</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1089</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>3850</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4676</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1473</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4291</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2561</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12119</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7354</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>18534</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,32%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8,08%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,37%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7541</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4095</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>12106</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>8,01%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,86%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>7569</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19272</t>
+          <t>12130</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20195</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13410</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>27417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,66%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25976</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18859</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>34338</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>28,55%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,73%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>37,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>26274</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>19224</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33518</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27,92%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>35,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>27157</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>20510</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35458</t>
+          <t>35774</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>52892</t>
+          <t>53133</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42114</t>
+          <t>43106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>63970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>40767</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>32468</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>48873</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>44,81%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>35,69%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>53,72%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>41140</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>34125</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>49323</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>43,71%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>36,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,41%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>42217</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>34641</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51783</t>
+          <t>51269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>83479</t>
+          <t>82983</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72859</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>96093</t>
+          <t>94899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7168</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4137</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>11565</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4,55%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>12,71%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>14050</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>9156</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>20794</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>22,09%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>20362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>20831</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15172</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>30707</t>
+          <t>28584</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>3775</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9164</t>
+          <t>8483</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9334</t>
+          <t>9891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8097</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3911</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14031</t>
+          <t>14113</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>90980</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>94116</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>96054</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>96054</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>96054</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>95043</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>95043</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>95043</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>270</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>189159</t>
+          <t>187033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1856</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>522</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5124</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,1%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>1834</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>434</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>4879</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>9,41%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2190</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>356</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5777</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>7887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7395</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3796</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>12945</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>13,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>6,74%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>22,99%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>4672</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>8492</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>9,01%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>1937</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12268</t>
+          <t>8791</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>11977</t>
+          <t>12178</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>18076</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>12383</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>24798</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>32,11%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>44,05%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>10041</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>5826</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>15673</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,36%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30,22%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18928</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12924</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25899</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>28971</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21229</t>
+          <t>21530</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>38162</t>
+          <t>39133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22802</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>17071</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>29724</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>40,5%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>30,32%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>52,8%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>26942</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20719</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>33367</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>51,95%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>64,34%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>25473</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33152</t>
+          <t>34894</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>52415</t>
+          <t>50868</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43224</t>
+          <t>41376</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>62360</t>
+          <t>60375</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>45,6%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>55,0%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>4076</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>7788</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>13,83%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>7482</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>4013</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>13042</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>7,74%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6614</t>
+          <t>7219</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14096</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2093</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>5467</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3,72%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>890</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3101</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2667</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>2578</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>834</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6379</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>56297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>51861</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>53482</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>53482</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>53482</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>63087</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>63087</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>63087</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>158</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>114948</t>
+          <t>109779</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>4139</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1896</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>8276</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>6805</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>3165</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>11750</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>6731</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6787</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>26714</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>19169</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>36875</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>9,58%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,44%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>12895</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>6869</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>19320</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8,9%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39318</t>
+          <t>18785</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>41660</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29563</t>
+          <t>31153</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>53442</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>52556</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>41120</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>69241</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>26,27%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>20,56%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>34,62%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>30080</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>18713</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>42352</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>19,51%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>55250</t>
+          <t>29698</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>41802</t>
+          <t>22320</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>72063</t>
+          <t>39523</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>85329</t>
+          <t>82254</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>65544</t>
+          <t>66753</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>104589</t>
+          <t>97800</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>78360</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>66069</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>93085</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>39,18%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>33,03%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>46,54%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>129</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>85880</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>56962</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>105273</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>39,56%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>26,24%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>48,5%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>83337</t>
+          <t>84992</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69639</t>
+          <t>71790</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98301</t>
+          <t>94910</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>53,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>169217</t>
+          <t>163353</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>137608</t>
+          <t>146470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>192966</t>
+          <t>180847</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>43,21%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>47,84%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>31581</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>23176</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>40640</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>15,79%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11,59%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>72105</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>45460</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>122451</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>33,22%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>36100</t>
+          <t>34817</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>27030</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>46159</t>
+          <t>47295</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>108204</t>
+          <t>66399</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>80229</t>
+          <t>55321</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>172034</t>
+          <t>79994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6676</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>3534</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>13069</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>9300</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>4793</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>15926</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>2,21%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>7,34%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14697</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11468</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28120</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>200026</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>217065</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>177995</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>177995</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>177995</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>216078</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>216078</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>216078</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>556</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>433143</t>
+          <t>378022</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1766</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>299</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>237</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6556</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>3807</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9259</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>15516</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>25015</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>8844</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>4801</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>14878</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>7,41%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>12,46%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>15152</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>26140</t>
+          <t>15354</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>23997</t>
+          <t>24829</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>35651</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>29495</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>21924</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>39906</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>26,97%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>24650</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>17481</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>32254</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>20,64%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>27,01%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>31574</t>
+          <t>26686</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>21988</t>
+          <t>19972</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>42864</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>56224</t>
+          <t>56181</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44184</t>
+          <t>45145</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>70817</t>
+          <t>68653</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,74%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>72357</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>56202</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>84410</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>48,91%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>37,99%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>57,05%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>64930</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>55324</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>74228</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>54,37%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>46,32%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>62,15%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>77644</t>
+          <t>63349</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>58831</t>
+          <t>53878</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>90545</t>
+          <t>72447</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>53,35%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>142574</t>
+          <t>135705</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>122922</t>
+          <t>116562</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>159532</t>
+          <t>150599</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -4352,72 +4352,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>26805</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>16611</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>51691</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>11,23%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>34,94%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>14606</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>9362</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>21339</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>12,23%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>7,84%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>17,87%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>32757</t>
+          <t>13671</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>20104</t>
+          <t>8769</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60616</t>
+          <t>19641</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>47363</t>
+          <t>40476</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>76877</t>
+          <t>67336</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>5981</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>4632</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>2134</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>9009</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1763</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6833</t>
+          <t>7156</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>7686</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>147945</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>119428</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>118731</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>118731</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>118731</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>162221</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>162221</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>162221</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>377</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>281650</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4695,72 +4695,72 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>1643</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>5186</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>7,59%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>3605</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2636</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>1737</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>383</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>5368</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>816</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6283</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4808,72 +4808,72 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>7968</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>4079</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>13880</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>20,33%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>4205</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>8336</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>12,1%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>7872</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>1899</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>14357</t>
+          <t>8488</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,32 +4883,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12310</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>19318</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,74%</t>
         </is>
       </c>
     </row>
@@ -4921,72 +4921,72 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>16023</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>10342</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>23332</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>34,17%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>10444</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>5914</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>17268</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>15,16%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>8,58%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>15961</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10599</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>19845</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>36054</t>
+          <t>38125</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -5034,72 +5034,72 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>34312</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>26778</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>41752</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>50,25%</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>39,21%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>61,14%</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>40582</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>32728</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>47259</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>58,9%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>47,5%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>68,6%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>42225</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>29615</t>
+          <t>33815</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>45211</t>
+          <t>48844</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>77572</t>
+          <t>76538</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>66553</t>
+          <t>65764</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>86659</t>
+          <t>85958</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>62,0%</t>
         </is>
       </c>
     </row>
@@ -5147,72 +5147,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>1794</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>10205</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>6,65%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>10412</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>6039</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>18309</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>26,58%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>11172</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>12938</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>10028</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>19773</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -5260,72 +5260,72 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>3803</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>8257</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>12,09%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>2274</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>6008</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>3,3%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>445</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>5826</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,22 +5335,22 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>6422</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>3124</t>
+          <t>3082</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -5373,74 +5373,74 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>68287</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>68895</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>70356</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>72003</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>72003</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>72003</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>189</t>
@@ -5448,17 +5448,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>140898</t>
+          <t>138644</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5490,72 +5490,72 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>10710</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>6430</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>16330</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>9346</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>21033</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>9710</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>21473</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,22 +5565,22 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>25444</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>20123</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>37023</t>
+          <t>33508</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5603,72 +5603,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>90883</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>76564</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>108486</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>15,82%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>55430</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>44346</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>69945</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>92934</t>
+          <t>54607</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>43942</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>111343</t>
+          <t>65641</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>148364</t>
+          <t>145490</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>129066</t>
+          <t>127852</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>171516</t>
+          <t>168070</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -5716,72 +5716,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>171833</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>150655</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>194315</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>25,06%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>21,97%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>28,33%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>124627</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>102473</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>143446</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>19,0%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>21,87%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>181898</t>
+          <t>130419</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>157980</t>
+          <t>113495</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>205107</t>
+          <t>149894</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>306524</t>
+          <t>302252</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>277411</t>
+          <t>276441</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>338280</t>
+          <t>330671</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,33%</t>
         </is>
       </c>
     </row>
@@ -5829,72 +5829,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>297910</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>270422</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>320618</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>43,44%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>39,43%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>46,75%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>449</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>307562</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>271187</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>333424</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>46,9%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>41,35%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>50,84%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>322817</t>
+          <t>309548</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>296622</t>
+          <t>287831</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>351722</t>
+          <t>333696</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>53,86%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5904,32 +5904,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>630378</t>
+          <t>607458</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>585076</t>
+          <t>575427</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>666563</t>
+          <t>638673</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>46,54%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -5942,72 +5942,72 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>90712</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>74778</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>120205</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>13,23%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>129897</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>99593</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>197961</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
-        <is>
-          <t>19,81%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>15,19%</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>106914</t>
+          <t>88200</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>88221</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>139811</t>
+          <t>103924</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>236811</t>
+          <t>178912</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>198835</t>
+          <t>156638</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>320662</t>
+          <t>205848</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>15,77%</t>
         </is>
       </c>
     </row>
@@ -6055,72 +6055,72 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>23738</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>17107</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>32853</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>3,46%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>4,79%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>23456</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>16576</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>32469</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>27445</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>19944</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>37937</t>
+          <t>30751</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>50901</t>
+          <t>45777</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>40725</t>
+          <t>36116</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>64144</t>
+          <t>57014</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -6168,74 +6168,74 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>685786</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>655827</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>619546</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>619546</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>619546</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I52" s="2" t="inlineStr">
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>951</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>744950</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>744950</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>744950</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
           <t>1877</t>
@@ -6243,17 +6243,17 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1400777</t>
+          <t>1305332</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">

--- a/data/trans_orig/IP24_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Clase-trans_orig.xlsx
@@ -1007,7 +1007,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1508,7 +1508,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2009,7 +2009,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2510,7 +2510,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -3011,7 +3011,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -3512,7 +3512,7 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -4013,7 +4013,7 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C50" s="5" t="n">
